--- a/output/risk_analysis.xlsx
+++ b/output/risk_analysis.xlsx
@@ -462,37 +462,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>17.36112455946959</v>
+        <v>23.11654397825395</v>
       </c>
       <c r="C2">
-        <v>24.58138375483678</v>
+        <v>24.67048045853365</v>
       </c>
       <c r="D2">
-        <v>0.7062712470795512</v>
+        <v>0.9370123138504917</v>
       </c>
       <c r="E2">
-        <v>-42.64455350815371</v>
+        <v>-40.3712787488076</v>
       </c>
       <c r="F2">
-        <v>0.04545719313806531</v>
+        <v>0.04063271491408972</v>
       </c>
       <c r="G2">
-        <v>0.3182687447422485</v>
+        <v>0.4740954841258979</v>
       </c>
       <c r="H2">
-        <v>1.174163707643312</v>
+        <v>1.044771147261729</v>
       </c>
       <c r="I2">
-        <v>-10.43392223510591</v>
+        <v>-9.488084856499537</v>
       </c>
       <c r="J2">
-        <v>-0.2667540547682339</v>
+        <v>0.06549849933728467</v>
       </c>
       <c r="K2">
-        <v>3.854340314328012</v>
+        <v>3.759009029457043</v>
       </c>
       <c r="L2">
-        <v>65.51724137931035</v>
+        <v>65.90909090909091</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -500,37 +500,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>1.064370870871492</v>
+        <v>9.474519256460539</v>
       </c>
       <c r="C3">
-        <v>26.43165074973891</v>
+        <v>24.86509612785037</v>
       </c>
       <c r="D3">
-        <v>0.04026880049790328</v>
+        <v>0.3810369044119046</v>
       </c>
       <c r="E3">
-        <v>-45.19664649007071</v>
+        <v>-37.72195050362881</v>
       </c>
       <c r="F3">
-        <v>0.05978974499301151</v>
+        <v>0.04713574365800696</v>
       </c>
       <c r="G3">
-        <v>0.01483491401125589</v>
+        <v>0.1675041507990702</v>
       </c>
       <c r="H3">
-        <v>1.61908111248436</v>
+        <v>1.296844059514964</v>
       </c>
       <c r="I3">
-        <v>-10.45204949613604</v>
+        <v>-9.970250873980584</v>
       </c>
       <c r="J3">
-        <v>-0.8614552765310829</v>
+        <v>0.09834259324673228</v>
       </c>
       <c r="K3">
-        <v>7.945884850999331</v>
+        <v>5.279233080986504</v>
       </c>
       <c r="L3">
-        <v>49.42528735632184</v>
+        <v>52.27272727272727</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -538,37 +538,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>-6.846996944325201</v>
+        <v>2.969313506701329</v>
       </c>
       <c r="C4">
-        <v>36.83197130336077</v>
+        <v>33.06710290353985</v>
       </c>
       <c r="D4">
-        <v>-0.1858981939340412</v>
+        <v>0.08979660284613149</v>
       </c>
       <c r="E4">
-        <v>-64.54539443251635</v>
+        <v>-62.27396138315407</v>
       </c>
       <c r="F4">
-        <v>0.09326810637339741</v>
+        <v>0.06771248955620045</v>
       </c>
       <c r="G4">
-        <v>-0.06117665522332429</v>
+        <v>0.03654315383275586</v>
       </c>
       <c r="H4">
-        <v>2.575128169698341</v>
+        <v>1.951240369395981</v>
       </c>
       <c r="I4">
-        <v>-15.42482945649187</v>
+        <v>-13.36794845194158</v>
       </c>
       <c r="J4">
-        <v>-1.808997605208844</v>
+        <v>-0.3064490184764623</v>
       </c>
       <c r="K4">
-        <v>12.51812740488587</v>
+        <v>6.430940720882875</v>
       </c>
       <c r="L4">
-        <v>49.42528735632184</v>
+        <v>52.27272727272727</v>
       </c>
     </row>
   </sheetData>
